--- a/premise/data/additional_inventories/lci-batteries-LiS.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-LiS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41DEF73-0BD7-DE4D-9CBD-9EB9FFE2BF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ADDE62-F391-1E48-B22D-C70267C828F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31560" yWindow="-860" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="23000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery - Li-S" sheetId="1" r:id="rId1"/>
@@ -1568,9 +1568,6 @@
     <t>battery, Li-S</t>
   </si>
   <si>
-    <t>This is a multi-output process, which produces dimethylchlorosilane (97%) but also trimethylchlorosilane (3%). The ecoinvent dataset for trimethylchlorosilane has been re-allocated to produce a proxy for dimethylchlorosilane production, based on a mass allocation. Note that, compared to the oroginal values in ecoinvent and also Wickerts et al., 2023, we have reduced the emission of methyl chloride, a potent ozone-depleting gas, to 1%, instead of 4.5%, which seems to ignore current efforts in limiting venting of such gases and promoting recovery instead. According to this report (https://www.chlorinated-solvents.eu/wp-content/uploads/2021/05/Dichloromethane-paper.pdf), the current leak rate in the EU is about 0.06%. Source: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141</t>
-  </si>
-  <si>
     <t>uncertainty type</t>
   </si>
   <si>
@@ -1584,6 +1581,9 @@
   </si>
   <si>
     <t>Original value in Wickerts et al., 2023 of 0.0412, representing a 4.5% leakage rate. This was reduced to 0.5% leakage rate. According to https://www.chlorinated-solvents.eu/wp-content/uploads/2021/05/Dichloromethane-paper.pdf, current leakage rate in the EU is 0.06%.</t>
+  </si>
+  <si>
+    <t>This is a multi-output process, which produces dimethylchlorosilane (97%) but also trimethylchlorosilane (3%). The ecoinvent dataset for trimethylchlorosilane has been re-allocated to produce a proxy for dimethylchlorosilane production, based on a mass allocation. Note that, compared to the original values in ecoinvent and also Wickerts et al., 2023, we have reduced the emission of methyl chloride, a potent ozone-depleting gas, to 0.5%, instead of 4.5%, with a min-max of 0.06%-4.1%, as it seems to ignore current efforts in limiting venting of such gases and promoting recovery instead. According to this report (https://www.chlorinated-solvents.eu/wp-content/uploads/2021/05/Dichloromethane-paper.pdf), the current leak rate in the EU is about 0.06%. Source for Li-S battery: Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. https://doi.org/10.1021/acssuschemeng.3c00141. Source for trimethylchlorosilane: https://pubs.acs.org/doi/10.1021/acssuschemeng.1c00376</t>
   </si>
 </sst>
 </file>
@@ -2930,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -3004,16 +3004,16 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
+        <v>458</v>
+      </c>
+      <c r="J75" t="s">
         <v>459</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>460</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>461</v>
-      </c>
-      <c r="L75" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -3423,7 +3423,7 @@
         <v>44</v>
       </c>
       <c r="H95" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I95">
         <v>5</v>
